--- a/Documentation/docs/Product Book/PPIQ_Backlog_v2_10_1_12Aug2026.xlsx
+++ b/Documentation/docs/Product Book/PPIQ_Backlog_v2_10_1_12Aug2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\PlantProcess-IQ\Documentation\docs\Product Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{64E556BD-97EC-4A46-8250-9CE501E3C3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{2E6E1F26-8C53-457F-A0C5-1A2F5D34CEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14397,38 +14397,38 @@
       </c>
     </row>
     <row r="169" spans="1:16" ht="120" x14ac:dyDescent="0.25">
-      <c r="A169" s="109" t="s">
+      <c r="A169" s="110" t="s">
         <v>849</v>
       </c>
-      <c r="B169" s="109" t="s">
+      <c r="B169" s="110" t="s">
         <v>618</v>
       </c>
-      <c r="C169" s="109" t="s">
+      <c r="C169" s="110" t="s">
         <v>850</v>
       </c>
-      <c r="D169" s="109" t="s">
+      <c r="D169" s="110" t="s">
         <v>851</v>
       </c>
-      <c r="E169" s="109" t="s">
+      <c r="E169" s="110" t="s">
         <v>358</v>
       </c>
-      <c r="F169" s="109" t="s">
+      <c r="F169" s="110" t="s">
         <v>852</v>
       </c>
-      <c r="G169" s="109" t="s">
+      <c r="G169" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="H169" s="109" t="s">
+      <c r="H169" s="110" t="s">
         <v>853</v>
       </c>
-      <c r="I169" s="109" t="s">
+      <c r="I169" s="110" t="s">
         <v>854</v>
       </c>
-      <c r="J169" s="109">
+      <c r="J169" s="110">
         <v>12</v>
       </c>
-      <c r="K169" s="109" t="s">
-        <v>230</v>
+      <c r="K169" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="L169" s="25" t="s">
         <v>527</v>
@@ -14447,38 +14447,38 @@
       </c>
     </row>
     <row r="170" spans="1:16" ht="90" x14ac:dyDescent="0.25">
-      <c r="A170" s="108" t="s">
+      <c r="A170" s="109" t="s">
         <v>856</v>
       </c>
-      <c r="B170" s="108" t="s">
+      <c r="B170" s="109" t="s">
         <v>618</v>
       </c>
-      <c r="C170" s="108" t="s">
+      <c r="C170" s="109" t="s">
         <v>850</v>
       </c>
-      <c r="D170" s="108" t="s">
+      <c r="D170" s="109" t="s">
         <v>857</v>
       </c>
-      <c r="E170" s="108" t="s">
+      <c r="E170" s="109" t="s">
         <v>358</v>
       </c>
-      <c r="F170" s="108" t="s">
+      <c r="F170" s="109" t="s">
         <v>858</v>
       </c>
-      <c r="G170" s="108" t="s">
+      <c r="G170" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="H170" s="108" t="s">
+      <c r="H170" s="109" t="s">
         <v>859</v>
       </c>
-      <c r="I170" s="108" t="s">
+      <c r="I170" s="109" t="s">
         <v>860</v>
       </c>
-      <c r="J170" s="108">
+      <c r="J170" s="109">
         <v>10</v>
       </c>
-      <c r="K170" s="108" t="s">
-        <v>240</v>
+      <c r="K170" s="109" t="s">
+        <v>230</v>
       </c>
       <c r="L170" s="16" t="s">
         <v>527</v>
